--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.133.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.133.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.133" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.133" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.133.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.133.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0133.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0133.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.133.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.133.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.133" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.133" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,18 +422,18 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="41" customWidth="1" min="14" max="14"/>
-    <col width="41" customWidth="1" min="15" max="15"/>
+    <col width="42" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -596,21 +596,21 @@
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>L139: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR | suspicious token(s): 4c (letter/digit mix) :: And for further relief ; pray subpÃ¦na, 4c.</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>L31: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: (And for further relief: pray subpa Ã¦ na, gc.</t>
-        </is>
-      </c>
+          <t>L139: suspicious token(s): 4c (letter/digit mix) :: And for further relief ; pray subpæna, 4c.</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L24: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: NOTE.â€”If 1</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]126 ORDERS OF JANUARY 1851.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]126 ORDERS OF JANUARY 1851.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L1: isolated marker/symbol line :: 126</t>
@@ -649,7 +649,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>112</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -658,16 +658,8 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L32: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: NorE.â€” This form may be varied according to the circumstances</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L58: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: NOTE.â€”This form may be varied according to the circumstances</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -717,16 +709,8 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L45: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: estate and payment of his share th Ã© reof.</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L77: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: intestates, of ---------,late of -------â€”, who died on</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -734,7 +718,11 @@
           <t>L41: isolated marker/symbol line :: 4.</t>
         </is>
       </c>
-      <c r="O4" s="1" t="inlineStr"/>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>L149: isolated marker/symbol line :: — ,</t>
+        </is>
+      </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr">
         <is>
@@ -758,12 +746,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -772,16 +760,8 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L76: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: And for further relief; pray subpa Ã¦ na, .</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L82: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: estate of the said ------1â€”, deceased, and that C. D.,</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -827,16 +807,8 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L126: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: (And for further relief: pray subpa Ã¦ na, gc.</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L92: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”â€”, but ne</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -848,7 +820,7 @@
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>L77: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: intestates, of ---------,late of -------â€”, who died on</t>
+          <t>L77: punctuation artifact: double/multiple hyphen :: intestates, of ---------,late of -------—, who died on</t>
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
@@ -882,16 +854,8 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L128: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: NorE.â€” This form may be varied according to the circumstances</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L93: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: about theâ€”</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
@@ -937,16 +901,8 @@
       <c r="G8" s="1" t="inlineStr"/>
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L149: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: estate and payment of his share th Ã© reof.</t>
-        </is>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L132: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: the (or the said A. B.â€™s share of the) personal estate of</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
@@ -958,7 +914,7 @@
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>L82: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: estate of the said ------1â€”, deceased, and that C. D.,</t>
+          <t>L82: punctuation artifact: double/multiple hyphen :: estate of the said ------1—, deceased, and that C. D.,</t>
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr"/>
@@ -992,16 +948,8 @@
       <c r="G9" s="1" t="inlineStr"/>
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L197: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: And for further relief; pray subpa Ã¦ na, .</t>
-        </is>
-      </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L139: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR | suspicious token(s): 4c (letter/digit mix) :: And for further relief ; pray subpÃ¦na, 4c.</t>
-        </is>
-      </c>
+      <c r="J9" s="1" t="inlineStr"/>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr"/>
@@ -1029,12 +977,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1044,11 +992,7 @@
       <c r="H10" s="1" t="inlineStr"/>
       <c r="I10" s="1" t="inlineStr"/>
       <c r="J10" s="1" t="inlineStr"/>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L149: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” ,</t>
-        </is>
-      </c>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr"/>
@@ -1077,7 +1021,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1116,7 +1060,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
